--- a/cim_sourcetype_inventory.xlsx
+++ b/cim_sourcetype_inventory.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JamesHBaxter\Dropbox\Programming\splunk-cim-reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD060941-8AFB-4AA5-AD38-6E14B849EDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B89FA1B-BD50-4696-9548-37DE59EA6DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28125" yWindow="2820" windowWidth="23400" windowHeight="19185" xr2:uid="{9B46642C-0618-4BD2-A18B-2F59CC5C4C41}"/>
+    <workbookView xWindow="-30615" yWindow="2820" windowWidth="24195" windowHeight="19545" xr2:uid="{6D0AD3CC-FA93-411A-89CE-D26E2C6D57D8}"/>
   </bookViews>
   <sheets>
     <sheet name="cim_sourcetype_inventory" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cim_sourcetype_inventory!$A$1:$J$850</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cim_sourcetype_inventory!$A$1:$J$886</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7816" uniqueCount="2771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8113" uniqueCount="2884">
   <si>
     <t>sourcetype</t>
   </si>
@@ -7993,6 +7993,9 @@
     <t>WinEventLog</t>
   </si>
   <si>
+    <t>Authentication.Authentication, Change.All_Changes, Endpoint.Ports, Endpoint.Processes, Endpoint.Registry, Endpoint.Services, Intrusion_Detection.IDS_Attacks, Malware.Malware_Operations, Updates.Updates</t>
+  </si>
+  <si>
     <t>Windows Event Log</t>
   </si>
   <si>
@@ -8335,7 +8338,343 @@
     <t>openSUSE / SLES zypper package manager log from /var/log/zypp/history - install/update/remove transactions on SUSE-family hosts.</t>
   </si>
   <si>
-    <t>Authentication.Authentication, Change.All_Changes, Endpoint.Ports, Endpoint.Processes, Endpoint.Registry, Endpoint.Services, Intrusion_Detection.IDS_Attacks, Malware.Malware_Operations, Updates.Updates</t>
+    <t>AzureLinuxBaseline-pre_install</t>
+  </si>
+  <si>
+    <t>Azure Linux baseline agent log</t>
+  </si>
+  <si>
+    <t>Azure guest-configuration / security-baseline agent activity on a Linux VM, captured before the baseline package finished installing (Splunk's -pre_install learned variant). Operational setup telemetry.</t>
+  </si>
+  <si>
+    <t>azure:compute:vm:instanceView</t>
+  </si>
+  <si>
+    <t>Azure VM instance view</t>
+  </si>
+  <si>
+    <t>Azure Resource Manager instance view for a Compute virtual machine - power/provisioning state, VM agent status, and per-disk/extension status. Feeds cloud asset inventory.</t>
+  </si>
+  <si>
+    <t>box:events</t>
+  </si>
+  <si>
+    <t>Box enterprise event log</t>
+  </si>
+  <si>
+    <t>Box Events API stream (admin and enterprise events) - file/folder access, sharing, login, and admin activity from the Splunk Add-on for Box. CASB-grade audit of the Box platform.</t>
+  </si>
+  <si>
+    <t>citrix:aaa</t>
+  </si>
+  <si>
+    <t>Citrix NetScaler AAA logs</t>
+  </si>
+  <si>
+    <t>Citrix NetScaler/ADC AAA (authentication, authorization, auditing) events - user logon/logoff to Gateway and VPN virtual servers and authentication-policy decisions. Feeds the Authentication data model.</t>
+  </si>
+  <si>
+    <t>citrix:netscaler:appfw</t>
+  </si>
+  <si>
+    <t>Web.Proxy, Intrusion_Detection.IDS_Attacks</t>
+  </si>
+  <si>
+    <t>Citrix NetScaler Application Firewall logs</t>
+  </si>
+  <si>
+    <t>Citrix NetScaler/ADC Application Firewall (WAF) events - signature and policy violations, blocked requests, and protected-URL hits. Feeds the Web and Intrusion_Detection data models.</t>
+  </si>
+  <si>
+    <t>citrix:netscaler:gateway</t>
+  </si>
+  <si>
+    <t>Authentication.Authentication, Network_Traffic.All_Traffic</t>
+  </si>
+  <si>
+    <t>Citrix NetScaler Gateway logs</t>
+  </si>
+  <si>
+    <t>Citrix NetScaler/ADC Gateway (SSL VPN / remote access) events - user session establishment and teardown, ICA proxy connections, and endpoint-analysis results. Feeds Authentication and Network_Traffic.</t>
+  </si>
+  <si>
+    <t>confluence-upgrade</t>
+  </si>
+  <si>
+    <t>Confluence upgrade log</t>
+  </si>
+  <si>
+    <t>Atlassian Confluence application upgrade/maintenance log - version migration and upgrade-task output written during a Confluence platform update. Operational.</t>
+  </si>
+  <si>
+    <t>db_software_repo_sync</t>
+  </si>
+  <si>
+    <t>Software repository sync log</t>
+  </si>
+  <si>
+    <t>Database/software repository synchronization job log - package or content mirror sync activity. Operational maintenance telemetry.</t>
+  </si>
+  <si>
+    <t>dependency-agent-install-too_small</t>
+  </si>
+  <si>
+    <t>Azure Dependency Agent install log</t>
+  </si>
+  <si>
+    <t>Azure Monitor Dependency Agent installation log on a Linux VM, captured as Splunk's -too_small learned sourcetype (sample below the sizing threshold). Operational install telemetry.</t>
+  </si>
+  <si>
+    <t>error-too_small</t>
+  </si>
+  <si>
+    <t>Generic error log (too_small)</t>
+  </si>
+  <si>
+    <t>Unclassified error output captured as Splunk's -too_small learned sourcetype when the sampled file was below the sizing threshold. Operational; no stable schema.</t>
+  </si>
+  <si>
+    <t>eucanalytics</t>
+  </si>
+  <si>
+    <t>End-user-computing analytics log</t>
+  </si>
+  <si>
+    <t>End-user-computing analytics telemetry (virtual desktop / published-app usage metrics) observed on Linux hosts. Operational; precise product origin is environment-specific.</t>
+  </si>
+  <si>
+    <t>freshclam</t>
+  </si>
+  <si>
+    <t>ClamAV freshclam updater log</t>
+  </si>
+  <si>
+    <t>ClamAV freshclam daemon log - antivirus signature-database update checks and downloads. Operational hygiene for the ClamAV engine; low direct detection value.</t>
+  </si>
+  <si>
+    <t>google:gcp:pubsub:audit:admin_activity</t>
+  </si>
+  <si>
+    <t>GCP audit via Pub/Sub - admin activity</t>
+  </si>
+  <si>
+    <t>GCP Cloud Audit Logs Admin Activity stream delivered through a Pub/Sub subscription - control-plane create/update/delete operations across GCP services with caller identity and authz decision. Primary Change source.</t>
+  </si>
+  <si>
+    <t>google:gcp:pubsub:audit:data_access</t>
+  </si>
+  <si>
+    <t>GCP audit via Pub/Sub - data access</t>
+  </si>
+  <si>
+    <t>GCP Cloud Audit Logs Data Access stream delivered through a Pub/Sub subscription - reads and metadata access to resource data, with caller identity. Feeds Data_Access and Authentication.</t>
+  </si>
+  <si>
+    <t>google:gcp:pubsub:audit:policy_denied</t>
+  </si>
+  <si>
+    <t>GCP audit via Pub/Sub - policy denied</t>
+  </si>
+  <si>
+    <t>GCP Cloud Audit Logs Policy Denied stream delivered through a Pub/Sub subscription - requests denied by a security policy (IAM deny, VPC Service Controls, org policy). Feeds Authentication as denied access.</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>Generic JSON sourcetype</t>
+  </si>
+  <si>
+    <t>Splunk generic JSON sourcetype - structured events parsed as JSON with no product-specific semantics. A format sourcetype, not tied to a technology family; no inherent CIM mapping.</t>
+  </si>
+  <si>
+    <t>location_services</t>
+  </si>
+  <si>
+    <t>Location services log</t>
+  </si>
+  <si>
+    <t>Location / geolocation service events (device or user location tracking). Security-tagged; the specific product origin is environment-specific.</t>
+  </si>
+  <si>
+    <t>map:cveid:kev</t>
+  </si>
+  <si>
+    <t>CISA</t>
+  </si>
+  <si>
+    <t>CVE-to-KEV mapping</t>
+  </si>
+  <si>
+    <t>Mapping of CVE identifiers to the CISA Known Exploited Vulnerabilities (KEV) catalog - enrichment associating detected CVEs with active-exploitation status. Supports vulnerability prioritization; lookup/enrichment, not a raw event stream.</t>
+  </si>
+  <si>
+    <t>scs-banner-selection</t>
+  </si>
+  <si>
+    <t>Login banner selection log</t>
+  </si>
+  <si>
+    <t>Host login / SSH banner selection script output. Operational; environment-specific component.</t>
+  </si>
+  <si>
+    <t>server</t>
+  </si>
+  <si>
+    <t>Generic server log</t>
+  </si>
+  <si>
+    <t>Generic 'server' sourcetype - catch-all for a server process log with no finer routing configured. No stable schema or CIM mapping.</t>
+  </si>
+  <si>
+    <t>skylight</t>
+  </si>
+  <si>
+    <t>Skylight log</t>
+  </si>
+  <si>
+    <t>Skylight application/agent log observed on Linux hosts (e.g. network/application performance analytics). Operational; specific product origin is environment-specific.</t>
+  </si>
+  <si>
+    <t>slwsconfigservice.log</t>
+  </si>
+  <si>
+    <t>SLWS config service log</t>
+  </si>
+  <si>
+    <t>SLWS configuration-service log file. Operational application telemetry; environment-specific component.</t>
+  </si>
+  <si>
+    <t>splunkapps</t>
+  </si>
+  <si>
+    <t>Splunk Applications and Technical Add-ons (TAs)</t>
+  </si>
+  <si>
+    <t>Splunk-installed applications and Technical Add-ons (TAs) packaging inputs, parsing, and knowledge objects. Operational platform inventory; no inherent CIM mapping or security relevance.</t>
+  </si>
+  <si>
+    <t>sssd_pac-too_small</t>
+  </si>
+  <si>
+    <t>SSSD PAC responder log (too_small)</t>
+  </si>
+  <si>
+    <t>SSSD PAC responder log captured as Splunk's -too_small learned sourcetype; semantically the sssd_pac MS-PAC/Kerberos authorization-data responder, sampled below the sizing threshold. Operational.</t>
+  </si>
+  <si>
+    <t>svagent</t>
+  </si>
+  <si>
+    <t>Azure Site Recovery agent log</t>
+  </si>
+  <si>
+    <t>Azure Site Recovery Mobility Service agent (svagent) log on a protected Linux server - replication-agent health and operations. Operational.</t>
+  </si>
+  <si>
+    <t>term</t>
+  </si>
+  <si>
+    <t>Terminal/term log</t>
+  </si>
+  <si>
+    <t>Generic 'term' sourcetype - terminal or session output captured with no finer routing. No stable schema or CIM mapping.</t>
+  </si>
+  <si>
+    <t>uarespawnd</t>
+  </si>
+  <si>
+    <t>uarespawnd daemon log</t>
+  </si>
+  <si>
+    <t>uarespawnd service log - a process respawn/supervision daemon observed on Linux hosts. Operational; environment-specific component.</t>
+  </si>
+  <si>
+    <t>ufw-too_small</t>
+  </si>
+  <si>
+    <t>UFW firewall log (too_small)</t>
+  </si>
+  <si>
+    <t>Uncomplicated Firewall (ufw) log captured as Splunk's -too_small learned sourcetype; same source as the ufw sourcetype but sampled below the sizing threshold. Operational.</t>
+  </si>
+  <si>
+    <t>uninstall</t>
+  </si>
+  <si>
+    <t>Uninstall log</t>
+  </si>
+  <si>
+    <t>Generic software uninstall log - package/application removal output. Operational install/change telemetry.</t>
+  </si>
+  <si>
+    <t>userdata</t>
+  </si>
+  <si>
+    <t>User-data / cloud-init log</t>
+  </si>
+  <si>
+    <t>Instance user-data / cloud-init provisioning-script output captured at boot. Operational provisioning telemetry; environment-specific content.</t>
+  </si>
+  <si>
+    <t>vsftpd</t>
+  </si>
+  <si>
+    <t>vsftpd FTP server log</t>
+  </si>
+  <si>
+    <t>Very Secure FTP Daemon (vsftpd) log - user authentication and file upload/download activity on Linux/Unix FTP servers. Feeds the Authentication data model.</t>
+  </si>
+  <si>
+    <t>windows_snare_syslog</t>
+  </si>
+  <si>
+    <t>Intersect Alliance</t>
+  </si>
+  <si>
+    <t>Snare Windows syslog</t>
+  </si>
+  <si>
+    <t>Windows Event Log forwarded as syslog by the Snare agent (Intersect Alliance) - security, system, and application channel events in syslog format. Equivalent content to WinEventLog; feeds Authentication and Change.</t>
+  </si>
+  <si>
+    <t>wiz:userAuditLogs</t>
+  </si>
+  <si>
+    <t>Wiz</t>
+  </si>
+  <si>
+    <t>Wiz user audit logs</t>
+  </si>
+  <si>
+    <t>Wiz CNAPP user audit log - console logins, user actions, and configuration changes within the Wiz platform. Administrative audit trail for the Wiz tenant.</t>
+  </si>
+  <si>
+    <t>wsp</t>
+  </si>
+  <si>
+    <t>wsp service log</t>
+  </si>
+  <si>
+    <t>wsp service log observed on Linux hosts. Operational; specific origin is environment-specific.</t>
+  </si>
+  <si>
+    <t>xrdp-sesman</t>
+  </si>
+  <si>
+    <t>xrdp</t>
+  </si>
+  <si>
+    <t>xrdp session manager log</t>
+  </si>
+  <si>
+    <t>xrdp-sesman session-manager log - RDP session authentication and session lifecycle on Linux xrdp servers. Feeds the Authentication data model.</t>
+  </si>
+  <si>
+    <t>xrdp server log</t>
+  </si>
+  <si>
+    <t>xrdp open-source RDP server log - inbound RDP connection handling and client sessions on Linux. Feeds Authentication and Network_Traffic.</t>
   </si>
 </sst>
 </file>
@@ -9196,19 +9535,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75FE4412-4F1A-4946-AFBE-25997494D9A7}">
-  <dimension ref="A1:J850"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B996BFE-96F1-4A8F-B1EF-82FB608B9579}">
+  <dimension ref="A1:J886"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.1796875" customWidth="1"/>
+    <col min="1" max="1" width="41.7265625" customWidth="1"/>
     <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="64.6328125" customWidth="1"/>
+    <col min="6" max="6" width="65.1796875" customWidth="1"/>
     <col min="7" max="7" width="19.36328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="49.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="168.36328125" customWidth="1"/>
+    <col min="9" max="9" width="160.7265625" customWidth="1"/>
     <col min="10" max="10" width="14.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -33230,16 +33569,16 @@
         <v>35</v>
       </c>
       <c r="F810" t="s">
-        <v>2770</v>
+        <v>2656</v>
       </c>
       <c r="G810" t="s">
         <v>37</v>
       </c>
       <c r="H810" t="s">
-        <v>2656</v>
+        <v>2657</v>
       </c>
       <c r="I810" t="s">
-        <v>2657</v>
+        <v>2658</v>
       </c>
       <c r="J810" t="s">
         <v>19</v>
@@ -33247,7 +33586,7 @@
     </row>
     <row r="811" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A811" t="s">
-        <v>2658</v>
+        <v>2659</v>
       </c>
       <c r="B811" t="s">
         <v>34</v>
@@ -33265,10 +33604,10 @@
         <v>37</v>
       </c>
       <c r="H811" t="s">
-        <v>2659</v>
+        <v>2660</v>
       </c>
       <c r="I811" t="s">
-        <v>2660</v>
+        <v>2661</v>
       </c>
       <c r="J811" t="s">
         <v>19</v>
@@ -33276,7 +33615,7 @@
     </row>
     <row r="812" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A812" t="s">
-        <v>2661</v>
+        <v>2662</v>
       </c>
       <c r="B812" t="s">
         <v>34</v>
@@ -33297,10 +33636,10 @@
         <v>37</v>
       </c>
       <c r="H812" t="s">
-        <v>2662</v>
+        <v>2663</v>
       </c>
       <c r="I812" t="s">
-        <v>2663</v>
+        <v>2664</v>
       </c>
       <c r="J812" t="s">
         <v>19</v>
@@ -33308,7 +33647,7 @@
     </row>
     <row r="813" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A813" t="s">
-        <v>2664</v>
+        <v>2665</v>
       </c>
       <c r="B813" t="s">
         <v>34</v>
@@ -33326,10 +33665,10 @@
         <v>37</v>
       </c>
       <c r="H813" t="s">
-        <v>2665</v>
+        <v>2666</v>
       </c>
       <c r="I813" t="s">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="J813" t="s">
         <v>19</v>
@@ -33337,7 +33676,7 @@
     </row>
     <row r="814" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A814" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="B814" t="s">
         <v>34</v>
@@ -33358,10 +33697,10 @@
         <v>37</v>
       </c>
       <c r="H814" t="s">
-        <v>2668</v>
+        <v>2669</v>
       </c>
       <c r="I814" t="s">
-        <v>2669</v>
+        <v>2670</v>
       </c>
       <c r="J814" t="s">
         <v>19</v>
@@ -33369,7 +33708,7 @@
     </row>
     <row r="815" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A815" t="s">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="B815" t="s">
         <v>34</v>
@@ -33390,10 +33729,10 @@
         <v>37</v>
       </c>
       <c r="H815" t="s">
-        <v>2671</v>
+        <v>2672</v>
       </c>
       <c r="I815" t="s">
-        <v>2672</v>
+        <v>2673</v>
       </c>
       <c r="J815" t="s">
         <v>19</v>
@@ -33401,7 +33740,7 @@
     </row>
     <row r="816" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A816" t="s">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="B816" t="s">
         <v>34</v>
@@ -33422,10 +33761,10 @@
         <v>37</v>
       </c>
       <c r="H816" t="s">
-        <v>2674</v>
+        <v>2675</v>
       </c>
       <c r="I816" t="s">
-        <v>2675</v>
+        <v>2676</v>
       </c>
       <c r="J816" t="s">
         <v>19</v>
@@ -33433,7 +33772,7 @@
     </row>
     <row r="817" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A817" t="s">
-        <v>2676</v>
+        <v>2677</v>
       </c>
       <c r="B817" t="s">
         <v>34</v>
@@ -33454,10 +33793,10 @@
         <v>37</v>
       </c>
       <c r="H817" t="s">
-        <v>2677</v>
+        <v>2678</v>
       </c>
       <c r="I817" t="s">
-        <v>2678</v>
+        <v>2679</v>
       </c>
       <c r="J817" t="s">
         <v>19</v>
@@ -33465,7 +33804,7 @@
     </row>
     <row r="818" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A818" t="s">
-        <v>2679</v>
+        <v>2680</v>
       </c>
       <c r="B818" t="s">
         <v>34</v>
@@ -33486,10 +33825,10 @@
         <v>37</v>
       </c>
       <c r="H818" t="s">
-        <v>2680</v>
+        <v>2681</v>
       </c>
       <c r="I818" t="s">
-        <v>2681</v>
+        <v>2682</v>
       </c>
       <c r="J818" t="s">
         <v>19</v>
@@ -33497,7 +33836,7 @@
     </row>
     <row r="819" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A819" t="s">
-        <v>2682</v>
+        <v>2683</v>
       </c>
       <c r="B819" t="s">
         <v>34</v>
@@ -33518,10 +33857,10 @@
         <v>37</v>
       </c>
       <c r="H819" t="s">
-        <v>2683</v>
+        <v>2684</v>
       </c>
       <c r="I819" t="s">
-        <v>2684</v>
+        <v>2685</v>
       </c>
       <c r="J819" t="s">
         <v>19</v>
@@ -33529,7 +33868,7 @@
     </row>
     <row r="820" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A820" t="s">
-        <v>2685</v>
+        <v>2686</v>
       </c>
       <c r="B820" t="s">
         <v>34</v>
@@ -33550,10 +33889,10 @@
         <v>37</v>
       </c>
       <c r="H820" t="s">
-        <v>2686</v>
+        <v>2687</v>
       </c>
       <c r="I820" t="s">
-        <v>2687</v>
+        <v>2688</v>
       </c>
       <c r="J820" t="s">
         <v>19</v>
@@ -33561,7 +33900,7 @@
     </row>
     <row r="821" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A821" t="s">
-        <v>2688</v>
+        <v>2689</v>
       </c>
       <c r="B821" t="s">
         <v>34</v>
@@ -33576,16 +33915,16 @@
         <v>35</v>
       </c>
       <c r="F821" t="s">
-        <v>2689</v>
+        <v>2690</v>
       </c>
       <c r="G821" t="s">
         <v>37</v>
       </c>
       <c r="H821" t="s">
-        <v>2690</v>
+        <v>2691</v>
       </c>
       <c r="I821" t="s">
-        <v>2691</v>
+        <v>2692</v>
       </c>
       <c r="J821" t="s">
         <v>19</v>
@@ -33593,7 +33932,7 @@
     </row>
     <row r="822" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A822" t="s">
-        <v>2692</v>
+        <v>2693</v>
       </c>
       <c r="B822" t="s">
         <v>34</v>
@@ -33614,10 +33953,10 @@
         <v>37</v>
       </c>
       <c r="H822" t="s">
-        <v>2693</v>
+        <v>2694</v>
       </c>
       <c r="I822" t="s">
-        <v>2694</v>
+        <v>2695</v>
       </c>
       <c r="J822" t="s">
         <v>19</v>
@@ -33625,7 +33964,7 @@
     </row>
     <row r="823" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A823" t="s">
-        <v>2695</v>
+        <v>2696</v>
       </c>
       <c r="B823" t="s">
         <v>34</v>
@@ -33646,10 +33985,10 @@
         <v>37</v>
       </c>
       <c r="H823" t="s">
-        <v>2696</v>
+        <v>2697</v>
       </c>
       <c r="I823" t="s">
-        <v>2697</v>
+        <v>2698</v>
       </c>
       <c r="J823" t="s">
         <v>19</v>
@@ -33657,7 +33996,7 @@
     </row>
     <row r="824" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A824" t="s">
-        <v>2698</v>
+        <v>2699</v>
       </c>
       <c r="B824" t="s">
         <v>34</v>
@@ -33678,10 +34017,10 @@
         <v>37</v>
       </c>
       <c r="H824" t="s">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="I824" t="s">
-        <v>2700</v>
+        <v>2701</v>
       </c>
       <c r="J824" t="s">
         <v>19</v>
@@ -33689,7 +34028,7 @@
     </row>
     <row r="825" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A825" t="s">
-        <v>2701</v>
+        <v>2702</v>
       </c>
       <c r="B825" t="s">
         <v>34</v>
@@ -33710,10 +34049,10 @@
         <v>37</v>
       </c>
       <c r="H825" t="s">
-        <v>2702</v>
+        <v>2703</v>
       </c>
       <c r="I825" t="s">
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="J825" t="s">
         <v>19</v>
@@ -33721,7 +34060,7 @@
     </row>
     <row r="826" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A826" t="s">
-        <v>2704</v>
+        <v>2705</v>
       </c>
       <c r="B826" t="s">
         <v>34</v>
@@ -33742,10 +34081,10 @@
         <v>37</v>
       </c>
       <c r="H826" t="s">
-        <v>2705</v>
+        <v>2706</v>
       </c>
       <c r="I826" t="s">
-        <v>2706</v>
+        <v>2707</v>
       </c>
       <c r="J826" t="s">
         <v>19</v>
@@ -33753,7 +34092,7 @@
     </row>
     <row r="827" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A827" t="s">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="B827" t="s">
         <v>34</v>
@@ -33771,10 +34110,10 @@
         <v>37</v>
       </c>
       <c r="H827" t="s">
-        <v>2708</v>
+        <v>2709</v>
       </c>
       <c r="I827" t="s">
-        <v>2709</v>
+        <v>2710</v>
       </c>
       <c r="J827" t="s">
         <v>19</v>
@@ -33782,7 +34121,7 @@
     </row>
     <row r="828" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A828" t="s">
-        <v>2710</v>
+        <v>2711</v>
       </c>
       <c r="B828" t="s">
         <v>34</v>
@@ -33800,10 +34139,10 @@
         <v>37</v>
       </c>
       <c r="H828" t="s">
-        <v>2711</v>
+        <v>2712</v>
       </c>
       <c r="I828" t="s">
-        <v>2712</v>
+        <v>2713</v>
       </c>
       <c r="J828" t="s">
         <v>19</v>
@@ -33811,7 +34150,7 @@
     </row>
     <row r="829" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A829" t="s">
-        <v>2713</v>
+        <v>2714</v>
       </c>
       <c r="B829" t="s">
         <v>169</v>
@@ -33829,10 +34168,10 @@
         <v>2541</v>
       </c>
       <c r="H829" t="s">
-        <v>2714</v>
+        <v>2715</v>
       </c>
       <c r="I829" t="s">
-        <v>2715</v>
+        <v>2716</v>
       </c>
       <c r="J829" t="s">
         <v>19</v>
@@ -33840,7 +34179,7 @@
     </row>
     <row r="830" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A830" t="s">
-        <v>2716</v>
+        <v>2717</v>
       </c>
       <c r="B830" t="s">
         <v>11</v>
@@ -33858,10 +34197,10 @@
         <v>84</v>
       </c>
       <c r="H830" t="s">
-        <v>2717</v>
+        <v>2718</v>
       </c>
       <c r="I830" t="s">
-        <v>2718</v>
+        <v>2719</v>
       </c>
       <c r="J830" t="s">
         <v>19</v>
@@ -33869,7 +34208,7 @@
     </row>
     <row r="831" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A831" t="s">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="B831" t="s">
         <v>34</v>
@@ -33887,10 +34226,10 @@
         <v>37</v>
       </c>
       <c r="H831" t="s">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="I831" t="s">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="J831" t="s">
         <v>19</v>
@@ -33898,7 +34237,7 @@
     </row>
     <row r="832" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A832" t="s">
-        <v>2722</v>
+        <v>2723</v>
       </c>
       <c r="B832" t="s">
         <v>34</v>
@@ -33913,16 +34252,16 @@
         <v>35</v>
       </c>
       <c r="F832" t="s">
-        <v>2770</v>
+        <v>2656</v>
       </c>
       <c r="G832" t="s">
         <v>37</v>
       </c>
       <c r="H832" t="s">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="I832" t="s">
-        <v>2724</v>
+        <v>2725</v>
       </c>
       <c r="J832" t="s">
         <v>19</v>
@@ -33930,7 +34269,7 @@
     </row>
     <row r="833" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A833" t="s">
-        <v>2725</v>
+        <v>2726</v>
       </c>
       <c r="B833" t="s">
         <v>34</v>
@@ -33945,16 +34284,16 @@
         <v>35</v>
       </c>
       <c r="F833" t="s">
-        <v>2726</v>
+        <v>2727</v>
       </c>
       <c r="G833" t="s">
         <v>37</v>
       </c>
       <c r="H833" t="s">
-        <v>2727</v>
+        <v>2728</v>
       </c>
       <c r="I833" t="s">
-        <v>2728</v>
+        <v>2729</v>
       </c>
       <c r="J833" t="s">
         <v>19</v>
@@ -33962,7 +34301,7 @@
     </row>
     <row r="834" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A834" t="s">
-        <v>2729</v>
+        <v>2730</v>
       </c>
       <c r="B834" t="s">
         <v>34</v>
@@ -33985,7 +34324,7 @@
     </row>
     <row r="835" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A835" t="s">
-        <v>2730</v>
+        <v>2731</v>
       </c>
       <c r="B835" t="s">
         <v>34</v>
@@ -33996,7 +34335,7 @@
     </row>
     <row r="836" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A836" t="s">
-        <v>2731</v>
+        <v>2732</v>
       </c>
       <c r="B836" t="s">
         <v>34</v>
@@ -34007,7 +34346,7 @@
     </row>
     <row r="837" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A837" t="s">
-        <v>2732</v>
+        <v>2733</v>
       </c>
       <c r="B837" t="s">
         <v>34</v>
@@ -34018,7 +34357,7 @@
     </row>
     <row r="838" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A838" t="s">
-        <v>2733</v>
+        <v>2734</v>
       </c>
       <c r="B838" t="s">
         <v>34</v>
@@ -34032,7 +34371,7 @@
     </row>
     <row r="839" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A839" t="s">
-        <v>2734</v>
+        <v>2735</v>
       </c>
       <c r="B839" t="s">
         <v>34</v>
@@ -34052,7 +34391,7 @@
     </row>
     <row r="840" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A840" t="s">
-        <v>2735</v>
+        <v>2736</v>
       </c>
       <c r="B840" t="s">
         <v>34</v>
@@ -34063,7 +34402,7 @@
     </row>
     <row r="841" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A841" t="s">
-        <v>2736</v>
+        <v>2737</v>
       </c>
       <c r="B841" t="s">
         <v>11</v>
@@ -34078,10 +34417,10 @@
         <v>84</v>
       </c>
       <c r="H841" t="s">
-        <v>2737</v>
+        <v>2738</v>
       </c>
       <c r="I841" t="s">
-        <v>2738</v>
+        <v>2739</v>
       </c>
       <c r="J841" t="s">
         <v>19</v>
@@ -34089,7 +34428,7 @@
     </row>
     <row r="842" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A842" t="s">
-        <v>2739</v>
+        <v>2740</v>
       </c>
       <c r="B842" t="s">
         <v>12</v>
@@ -34110,10 +34449,10 @@
         <v>1227</v>
       </c>
       <c r="H842" t="s">
-        <v>2740</v>
+        <v>2741</v>
       </c>
       <c r="I842" t="s">
-        <v>2741</v>
+        <v>2742</v>
       </c>
       <c r="J842" t="s">
         <v>19</v>
@@ -34121,7 +34460,7 @@
     </row>
     <row r="843" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A843" t="s">
-        <v>2742</v>
+        <v>2743</v>
       </c>
       <c r="B843" t="s">
         <v>12</v>
@@ -34139,13 +34478,13 @@
         <v>15</v>
       </c>
       <c r="G843" t="s">
-        <v>2743</v>
+        <v>2744</v>
       </c>
       <c r="H843" t="s">
-        <v>2744</v>
+        <v>2745</v>
       </c>
       <c r="I843" t="s">
-        <v>2745</v>
+        <v>2746</v>
       </c>
       <c r="J843" t="s">
         <v>19</v>
@@ -34153,7 +34492,7 @@
     </row>
     <row r="844" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A844" t="s">
-        <v>2746</v>
+        <v>2747</v>
       </c>
       <c r="B844" t="s">
         <v>11</v>
@@ -34171,10 +34510,10 @@
         <v>84</v>
       </c>
       <c r="H844" t="s">
-        <v>2747</v>
+        <v>2748</v>
       </c>
       <c r="I844" t="s">
-        <v>2748</v>
+        <v>2749</v>
       </c>
       <c r="J844" t="s">
         <v>19</v>
@@ -34182,7 +34521,7 @@
     </row>
     <row r="845" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A845" t="s">
-        <v>2749</v>
+        <v>2750</v>
       </c>
       <c r="B845" t="s">
         <v>21</v>
@@ -34197,13 +34536,13 @@
         <v>899</v>
       </c>
       <c r="G845" t="s">
-        <v>2750</v>
+        <v>2751</v>
       </c>
       <c r="H845" t="s">
-        <v>2751</v>
+        <v>2752</v>
       </c>
       <c r="I845" t="s">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="J845" t="s">
         <v>19</v>
@@ -34211,7 +34550,7 @@
     </row>
     <row r="846" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A846" t="s">
-        <v>2753</v>
+        <v>2754</v>
       </c>
       <c r="B846" t="s">
         <v>169</v>
@@ -34232,10 +34571,10 @@
         <v>615</v>
       </c>
       <c r="H846" t="s">
-        <v>2754</v>
+        <v>2755</v>
       </c>
       <c r="I846" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="J846" t="s">
         <v>19</v>
@@ -34243,7 +34582,7 @@
     </row>
     <row r="847" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A847" t="s">
-        <v>2756</v>
+        <v>2757</v>
       </c>
       <c r="B847" t="s">
         <v>21</v>
@@ -34261,10 +34600,10 @@
         <v>23</v>
       </c>
       <c r="H847" t="s">
-        <v>2757</v>
+        <v>2758</v>
       </c>
       <c r="I847" t="s">
-        <v>2758</v>
+        <v>2759</v>
       </c>
       <c r="J847" t="s">
         <v>19</v>
@@ -34272,7 +34611,7 @@
     </row>
     <row r="848" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A848" t="s">
-        <v>2759</v>
+        <v>2760</v>
       </c>
       <c r="B848" t="s">
         <v>21</v>
@@ -34287,13 +34626,13 @@
         <v>15</v>
       </c>
       <c r="G848" t="s">
-        <v>2760</v>
+        <v>2761</v>
       </c>
       <c r="H848" t="s">
-        <v>2761</v>
+        <v>2762</v>
       </c>
       <c r="I848" t="s">
-        <v>2762</v>
+        <v>2763</v>
       </c>
       <c r="J848" t="s">
         <v>19</v>
@@ -34301,7 +34640,7 @@
     </row>
     <row r="849" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A849" t="s">
-        <v>2763</v>
+        <v>2764</v>
       </c>
       <c r="B849" t="s">
         <v>169</v>
@@ -34319,13 +34658,13 @@
         <v>602</v>
       </c>
       <c r="G849" t="s">
-        <v>2764</v>
+        <v>2765</v>
       </c>
       <c r="H849" t="s">
-        <v>2765</v>
+        <v>2766</v>
       </c>
       <c r="I849" t="s">
-        <v>2766</v>
+        <v>2767</v>
       </c>
       <c r="J849" t="s">
         <v>19</v>
@@ -34333,7 +34672,7 @@
     </row>
     <row r="850" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A850" t="s">
-        <v>2767</v>
+        <v>2768</v>
       </c>
       <c r="B850" t="s">
         <v>11</v>
@@ -34351,17 +34690,980 @@
         <v>84</v>
       </c>
       <c r="H850" t="s">
-        <v>2768</v>
+        <v>2769</v>
       </c>
       <c r="I850" t="s">
-        <v>2769</v>
+        <v>2770</v>
       </c>
       <c r="J850" t="s">
         <v>19</v>
       </c>
     </row>
+    <row r="851" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A851" t="s">
+        <v>2771</v>
+      </c>
+      <c r="B851" t="s">
+        <v>11</v>
+      </c>
+      <c r="C851" t="s">
+        <v>41</v>
+      </c>
+      <c r="E851" t="s">
+        <v>42</v>
+      </c>
+      <c r="G851" t="s">
+        <v>37</v>
+      </c>
+      <c r="H851" t="s">
+        <v>2772</v>
+      </c>
+      <c r="I851" t="s">
+        <v>2773</v>
+      </c>
+      <c r="J851" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="852" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A852" t="s">
+        <v>2774</v>
+      </c>
+      <c r="B852" t="s">
+        <v>53</v>
+      </c>
+      <c r="C852" t="s">
+        <v>159</v>
+      </c>
+      <c r="D852" t="s">
+        <v>215</v>
+      </c>
+      <c r="E852" t="s">
+        <v>14</v>
+      </c>
+      <c r="F852" t="s">
+        <v>330</v>
+      </c>
+      <c r="G852" t="s">
+        <v>37</v>
+      </c>
+      <c r="H852" t="s">
+        <v>2775</v>
+      </c>
+      <c r="I852" t="s">
+        <v>2776</v>
+      </c>
+      <c r="J852" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="853" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A853" t="s">
+        <v>2777</v>
+      </c>
+      <c r="B853" t="s">
+        <v>12</v>
+      </c>
+      <c r="C853" t="s">
+        <v>12</v>
+      </c>
+      <c r="D853" t="s">
+        <v>610</v>
+      </c>
+      <c r="E853" t="s">
+        <v>35</v>
+      </c>
+      <c r="F853" t="s">
+        <v>165</v>
+      </c>
+      <c r="G853" t="s">
+        <v>611</v>
+      </c>
+      <c r="H853" t="s">
+        <v>2778</v>
+      </c>
+      <c r="I853" t="s">
+        <v>2779</v>
+      </c>
+      <c r="J853" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="854" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A854" t="s">
+        <v>2780</v>
+      </c>
+      <c r="B854" t="s">
+        <v>169</v>
+      </c>
+      <c r="C854" t="s">
+        <v>12</v>
+      </c>
+      <c r="D854" t="s">
+        <v>459</v>
+      </c>
+      <c r="E854" t="s">
+        <v>14</v>
+      </c>
+      <c r="F854" t="s">
+        <v>15</v>
+      </c>
+      <c r="G854" t="s">
+        <v>729</v>
+      </c>
+      <c r="H854" t="s">
+        <v>2781</v>
+      </c>
+      <c r="I854" t="s">
+        <v>2782</v>
+      </c>
+      <c r="J854" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="855" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A855" t="s">
+        <v>2783</v>
+      </c>
+      <c r="B855" t="s">
+        <v>169</v>
+      </c>
+      <c r="C855" t="s">
+        <v>12</v>
+      </c>
+      <c r="D855" t="s">
+        <v>70</v>
+      </c>
+      <c r="E855" t="s">
+        <v>35</v>
+      </c>
+      <c r="F855" t="s">
+        <v>2784</v>
+      </c>
+      <c r="G855" t="s">
+        <v>729</v>
+      </c>
+      <c r="H855" t="s">
+        <v>2785</v>
+      </c>
+      <c r="I855" t="s">
+        <v>2786</v>
+      </c>
+      <c r="J855" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="856" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A856" t="s">
+        <v>2787</v>
+      </c>
+      <c r="B856" t="s">
+        <v>169</v>
+      </c>
+      <c r="C856" t="s">
+        <v>12</v>
+      </c>
+      <c r="D856" t="s">
+        <v>459</v>
+      </c>
+      <c r="E856" t="s">
+        <v>35</v>
+      </c>
+      <c r="F856" t="s">
+        <v>2788</v>
+      </c>
+      <c r="G856" t="s">
+        <v>729</v>
+      </c>
+      <c r="H856" t="s">
+        <v>2789</v>
+      </c>
+      <c r="I856" t="s">
+        <v>2790</v>
+      </c>
+      <c r="J856" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="857" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A857" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B857" t="s">
+        <v>11</v>
+      </c>
+      <c r="C857" t="s">
+        <v>41</v>
+      </c>
+      <c r="E857" t="s">
+        <v>201</v>
+      </c>
+      <c r="G857" t="s">
+        <v>593</v>
+      </c>
+      <c r="H857" t="s">
+        <v>2792</v>
+      </c>
+      <c r="I857" t="s">
+        <v>2793</v>
+      </c>
+      <c r="J857" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="858" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A858" t="s">
+        <v>2794</v>
+      </c>
+      <c r="B858" t="s">
+        <v>11</v>
+      </c>
+      <c r="C858" t="s">
+        <v>41</v>
+      </c>
+      <c r="E858" t="s">
+        <v>201</v>
+      </c>
+      <c r="H858" t="s">
+        <v>2795</v>
+      </c>
+      <c r="I858" t="s">
+        <v>2796</v>
+      </c>
+      <c r="J858" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="859" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A859" t="s">
+        <v>2797</v>
+      </c>
+      <c r="B859" t="s">
+        <v>11</v>
+      </c>
+      <c r="C859" t="s">
+        <v>41</v>
+      </c>
+      <c r="E859" t="s">
+        <v>201</v>
+      </c>
+      <c r="G859" t="s">
+        <v>37</v>
+      </c>
+      <c r="H859" t="s">
+        <v>2798</v>
+      </c>
+      <c r="I859" t="s">
+        <v>2799</v>
+      </c>
+      <c r="J859" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="860" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A860" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B860" t="s">
+        <v>11</v>
+      </c>
+      <c r="C860" t="s">
+        <v>41</v>
+      </c>
+      <c r="E860" t="s">
+        <v>201</v>
+      </c>
+      <c r="H860" t="s">
+        <v>2801</v>
+      </c>
+      <c r="I860" t="s">
+        <v>2802</v>
+      </c>
+      <c r="J860" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="861" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A861" t="s">
+        <v>2803</v>
+      </c>
+      <c r="B861" t="s">
+        <v>11</v>
+      </c>
+      <c r="C861" t="s">
+        <v>41</v>
+      </c>
+      <c r="E861" t="s">
+        <v>42</v>
+      </c>
+      <c r="H861" t="s">
+        <v>2804</v>
+      </c>
+      <c r="I861" t="s">
+        <v>2805</v>
+      </c>
+      <c r="J861" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="862" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A862" t="s">
+        <v>2806</v>
+      </c>
+      <c r="B862" t="s">
+        <v>11</v>
+      </c>
+      <c r="C862" t="s">
+        <v>41</v>
+      </c>
+      <c r="E862" t="s">
+        <v>42</v>
+      </c>
+      <c r="G862" t="s">
+        <v>736</v>
+      </c>
+      <c r="H862" t="s">
+        <v>2807</v>
+      </c>
+      <c r="I862" t="s">
+        <v>2808</v>
+      </c>
+      <c r="J862" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="863" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A863" t="s">
+        <v>2809</v>
+      </c>
+      <c r="B863" t="s">
+        <v>772</v>
+      </c>
+      <c r="C863" t="s">
+        <v>159</v>
+      </c>
+      <c r="D863" t="s">
+        <v>215</v>
+      </c>
+      <c r="E863" t="s">
+        <v>35</v>
+      </c>
+      <c r="F863" t="s">
+        <v>165</v>
+      </c>
+      <c r="G863" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H863" t="s">
+        <v>2810</v>
+      </c>
+      <c r="I863" t="s">
+        <v>2811</v>
+      </c>
+      <c r="J863" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="864" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A864" t="s">
+        <v>2812</v>
+      </c>
+      <c r="B864" t="s">
+        <v>772</v>
+      </c>
+      <c r="C864" t="s">
+        <v>12</v>
+      </c>
+      <c r="D864" t="s">
+        <v>215</v>
+      </c>
+      <c r="E864" t="s">
+        <v>35</v>
+      </c>
+      <c r="F864" t="s">
+        <v>904</v>
+      </c>
+      <c r="G864" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H864" t="s">
+        <v>2813</v>
+      </c>
+      <c r="I864" t="s">
+        <v>2814</v>
+      </c>
+      <c r="J864" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="865" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A865" t="s">
+        <v>2815</v>
+      </c>
+      <c r="B865" t="s">
+        <v>772</v>
+      </c>
+      <c r="C865" t="s">
+        <v>12</v>
+      </c>
+      <c r="D865" t="s">
+        <v>215</v>
+      </c>
+      <c r="E865" t="s">
+        <v>14</v>
+      </c>
+      <c r="F865" t="s">
+        <v>15</v>
+      </c>
+      <c r="G865" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H865" t="s">
+        <v>2816</v>
+      </c>
+      <c r="I865" t="s">
+        <v>2817</v>
+      </c>
+      <c r="J865" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="866" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A866" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C866" t="s">
+        <v>41</v>
+      </c>
+      <c r="E866" t="s">
+        <v>201</v>
+      </c>
+      <c r="H866" t="s">
+        <v>2819</v>
+      </c>
+      <c r="I866" t="s">
+        <v>2820</v>
+      </c>
+      <c r="J866" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="867" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A867" t="s">
+        <v>2821</v>
+      </c>
+      <c r="B867" t="s">
+        <v>12</v>
+      </c>
+      <c r="C867" t="s">
+        <v>12</v>
+      </c>
+      <c r="E867" t="s">
+        <v>42</v>
+      </c>
+      <c r="H867" t="s">
+        <v>2822</v>
+      </c>
+      <c r="I867" t="s">
+        <v>2823</v>
+      </c>
+      <c r="J867" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="868" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A868" t="s">
+        <v>2824</v>
+      </c>
+      <c r="B868" t="s">
+        <v>12</v>
+      </c>
+      <c r="C868" t="s">
+        <v>12</v>
+      </c>
+      <c r="D868" t="s">
+        <v>286</v>
+      </c>
+      <c r="E868" t="s">
+        <v>14</v>
+      </c>
+      <c r="G868" t="s">
+        <v>2825</v>
+      </c>
+      <c r="H868" t="s">
+        <v>2826</v>
+      </c>
+      <c r="I868" t="s">
+        <v>2827</v>
+      </c>
+      <c r="J868" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="869" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A869" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B869" t="s">
+        <v>11</v>
+      </c>
+      <c r="C869" t="s">
+        <v>41</v>
+      </c>
+      <c r="E869" t="s">
+        <v>201</v>
+      </c>
+      <c r="H869" t="s">
+        <v>2829</v>
+      </c>
+      <c r="I869" t="s">
+        <v>2830</v>
+      </c>
+      <c r="J869" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="870" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A870" t="s">
+        <v>2831</v>
+      </c>
+      <c r="B870" t="s">
+        <v>11</v>
+      </c>
+      <c r="C870" t="s">
+        <v>41</v>
+      </c>
+      <c r="E870" t="s">
+        <v>201</v>
+      </c>
+      <c r="H870" t="s">
+        <v>2832</v>
+      </c>
+      <c r="I870" t="s">
+        <v>2833</v>
+      </c>
+      <c r="J870" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="871" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A871" t="s">
+        <v>2834</v>
+      </c>
+      <c r="B871" t="s">
+        <v>11</v>
+      </c>
+      <c r="C871" t="s">
+        <v>41</v>
+      </c>
+      <c r="E871" t="s">
+        <v>42</v>
+      </c>
+      <c r="H871" t="s">
+        <v>2835</v>
+      </c>
+      <c r="I871" t="s">
+        <v>2836</v>
+      </c>
+      <c r="J871" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="872" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A872" t="s">
+        <v>2837</v>
+      </c>
+      <c r="B872" t="s">
+        <v>11</v>
+      </c>
+      <c r="C872" t="s">
+        <v>41</v>
+      </c>
+      <c r="E872" t="s">
+        <v>201</v>
+      </c>
+      <c r="H872" t="s">
+        <v>2838</v>
+      </c>
+      <c r="I872" t="s">
+        <v>2839</v>
+      </c>
+      <c r="J872" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="873" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A873" t="s">
+        <v>2840</v>
+      </c>
+      <c r="B873" t="s">
+        <v>21</v>
+      </c>
+      <c r="C873" t="s">
+        <v>41</v>
+      </c>
+      <c r="E873" t="s">
+        <v>201</v>
+      </c>
+      <c r="G873" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H873" t="s">
+        <v>2841</v>
+      </c>
+      <c r="I873" t="s">
+        <v>2842</v>
+      </c>
+      <c r="J873" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="874" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A874" t="s">
+        <v>2843</v>
+      </c>
+      <c r="B874" t="s">
+        <v>11</v>
+      </c>
+      <c r="C874" t="s">
+        <v>41</v>
+      </c>
+      <c r="E874" t="s">
+        <v>42</v>
+      </c>
+      <c r="G874" t="s">
+        <v>1424</v>
+      </c>
+      <c r="H874" t="s">
+        <v>2844</v>
+      </c>
+      <c r="I874" t="s">
+        <v>2845</v>
+      </c>
+      <c r="J874" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="875" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A875" t="s">
+        <v>2846</v>
+      </c>
+      <c r="B875" t="s">
+        <v>11</v>
+      </c>
+      <c r="C875" t="s">
+        <v>41</v>
+      </c>
+      <c r="E875" t="s">
+        <v>42</v>
+      </c>
+      <c r="G875" t="s">
+        <v>37</v>
+      </c>
+      <c r="H875" t="s">
+        <v>2847</v>
+      </c>
+      <c r="I875" t="s">
+        <v>2848</v>
+      </c>
+      <c r="J875" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="876" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A876" t="s">
+        <v>2849</v>
+      </c>
+      <c r="B876" t="s">
+        <v>11</v>
+      </c>
+      <c r="C876" t="s">
+        <v>41</v>
+      </c>
+      <c r="E876" t="s">
+        <v>201</v>
+      </c>
+      <c r="H876" t="s">
+        <v>2850</v>
+      </c>
+      <c r="I876" t="s">
+        <v>2851</v>
+      </c>
+      <c r="J876" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="877" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A877" t="s">
+        <v>2852</v>
+      </c>
+      <c r="B877" t="s">
+        <v>11</v>
+      </c>
+      <c r="C877" t="s">
+        <v>41</v>
+      </c>
+      <c r="E877" t="s">
+        <v>201</v>
+      </c>
+      <c r="H877" t="s">
+        <v>2853</v>
+      </c>
+      <c r="I877" t="s">
+        <v>2854</v>
+      </c>
+      <c r="J877" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="878" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A878" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B878" t="s">
+        <v>11</v>
+      </c>
+      <c r="C878" t="s">
+        <v>41</v>
+      </c>
+      <c r="E878" t="s">
+        <v>42</v>
+      </c>
+      <c r="G878" t="s">
+        <v>84</v>
+      </c>
+      <c r="H878" t="s">
+        <v>2856</v>
+      </c>
+      <c r="I878" t="s">
+        <v>2857</v>
+      </c>
+      <c r="J878" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="879" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A879" t="s">
+        <v>2858</v>
+      </c>
+      <c r="B879" t="s">
+        <v>11</v>
+      </c>
+      <c r="C879" t="s">
+        <v>41</v>
+      </c>
+      <c r="E879" t="s">
+        <v>201</v>
+      </c>
+      <c r="H879" t="s">
+        <v>2859</v>
+      </c>
+      <c r="I879" t="s">
+        <v>2860</v>
+      </c>
+      <c r="J879" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="880" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A880" t="s">
+        <v>2861</v>
+      </c>
+      <c r="B880" t="s">
+        <v>11</v>
+      </c>
+      <c r="C880" t="s">
+        <v>41</v>
+      </c>
+      <c r="E880" t="s">
+        <v>201</v>
+      </c>
+      <c r="H880" t="s">
+        <v>2862</v>
+      </c>
+      <c r="I880" t="s">
+        <v>2863</v>
+      </c>
+      <c r="J880" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="881" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A881" t="s">
+        <v>2864</v>
+      </c>
+      <c r="B881" t="s">
+        <v>11</v>
+      </c>
+      <c r="C881" t="s">
+        <v>12</v>
+      </c>
+      <c r="E881" t="s">
+        <v>14</v>
+      </c>
+      <c r="F881" t="s">
+        <v>15</v>
+      </c>
+      <c r="G881" t="s">
+        <v>2864</v>
+      </c>
+      <c r="H881" t="s">
+        <v>2865</v>
+      </c>
+      <c r="I881" t="s">
+        <v>2866</v>
+      </c>
+      <c r="J881" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="882" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A882" t="s">
+        <v>2867</v>
+      </c>
+      <c r="B882" t="s">
+        <v>11</v>
+      </c>
+      <c r="C882" t="s">
+        <v>12</v>
+      </c>
+      <c r="D882" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E882" t="s">
+        <v>35</v>
+      </c>
+      <c r="F882" t="s">
+        <v>36</v>
+      </c>
+      <c r="G882" t="s">
+        <v>2868</v>
+      </c>
+      <c r="H882" t="s">
+        <v>2869</v>
+      </c>
+      <c r="I882" t="s">
+        <v>2870</v>
+      </c>
+      <c r="J882" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="883" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A883" t="s">
+        <v>2871</v>
+      </c>
+      <c r="B883" t="s">
+        <v>21</v>
+      </c>
+      <c r="C883" t="s">
+        <v>12</v>
+      </c>
+      <c r="D883" t="s">
+        <v>215</v>
+      </c>
+      <c r="E883" t="s">
+        <v>14</v>
+      </c>
+      <c r="F883" t="s">
+        <v>165</v>
+      </c>
+      <c r="G883" t="s">
+        <v>2872</v>
+      </c>
+      <c r="H883" t="s">
+        <v>2873</v>
+      </c>
+      <c r="I883" t="s">
+        <v>2874</v>
+      </c>
+      <c r="J883" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="884" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A884" t="s">
+        <v>2875</v>
+      </c>
+      <c r="B884" t="s">
+        <v>11</v>
+      </c>
+      <c r="C884" t="s">
+        <v>41</v>
+      </c>
+      <c r="E884" t="s">
+        <v>201</v>
+      </c>
+      <c r="H884" t="s">
+        <v>2876</v>
+      </c>
+      <c r="I884" t="s">
+        <v>2877</v>
+      </c>
+      <c r="J884" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="885" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A885" t="s">
+        <v>2878</v>
+      </c>
+      <c r="B885" t="s">
+        <v>11</v>
+      </c>
+      <c r="C885" t="s">
+        <v>12</v>
+      </c>
+      <c r="E885" t="s">
+        <v>14</v>
+      </c>
+      <c r="F885" t="s">
+        <v>15</v>
+      </c>
+      <c r="G885" t="s">
+        <v>2879</v>
+      </c>
+      <c r="H885" t="s">
+        <v>2880</v>
+      </c>
+      <c r="I885" t="s">
+        <v>2881</v>
+      </c>
+      <c r="J885" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="886" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A886" t="s">
+        <v>2879</v>
+      </c>
+      <c r="B886" t="s">
+        <v>11</v>
+      </c>
+      <c r="C886" t="s">
+        <v>12</v>
+      </c>
+      <c r="E886" t="s">
+        <v>14</v>
+      </c>
+      <c r="F886" t="s">
+        <v>2788</v>
+      </c>
+      <c r="G886" t="s">
+        <v>2879</v>
+      </c>
+      <c r="H886" t="s">
+        <v>2882</v>
+      </c>
+      <c r="I886" t="s">
+        <v>2883</v>
+      </c>
+      <c r="J886" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J850" xr:uid="{75FE4412-4F1A-4946-AFBE-25997494D9A7}"/>
+  <autoFilter ref="A1:J886" xr:uid="{4B996BFE-96F1-4A8F-B1EF-82FB608B9579}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>